--- a/formularios/Configuracion de Relaciones.xlsx
+++ b/formularios/Configuracion de Relaciones.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="19">
   <si>
     <t xml:space="preserve">Fecha </t>
   </si>
@@ -31,31 +31,43 @@
     <t>autoevaluacion</t>
   </si>
   <si>
-    <t>Julio Soria</t>
+    <t>Tom Hanks</t>
   </si>
   <si>
     <t>supervisor</t>
   </si>
   <si>
-    <t>Christian Aragon</t>
+    <t>Eusebio Pernia</t>
   </si>
   <si>
     <t>subordinado</t>
   </si>
   <si>
-    <t>Jorge Starper</t>
+    <t>Scarlett Johansson</t>
   </si>
   <si>
     <t>par_externo</t>
   </si>
   <si>
-    <t>Carlos  Chavez</t>
+    <t>Robert De Niro</t>
   </si>
   <si>
     <t>cliente</t>
   </si>
   <si>
-    <t>Ana Cordoba</t>
+    <t>Jesus Parra</t>
+  </si>
+  <si>
+    <t>Meryl Streep</t>
+  </si>
+  <si>
+    <t>Cate Blanchett</t>
+  </si>
+  <si>
+    <t>Denzel Washington</t>
+  </si>
+  <si>
+    <t>Leonardo DiCaprio</t>
   </si>
 </sst>
 </file>
@@ -96,7 +108,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -108,6 +120,9 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -325,6 +340,9 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="4" max="4" width="15.25"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
@@ -345,15 +363,15 @@
     </row>
     <row r="2">
       <c r="A2" s="2">
-        <v>46041.0</v>
+        <v>46050.0</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="4" t="s">
         <v>6</v>
       </c>
       <c r="E2" s="3">
@@ -362,15 +380,15 @@
     </row>
     <row r="3">
       <c r="A3" s="2">
-        <v>46042.0</v>
+        <v>46063.0</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="4" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="3">
@@ -379,15 +397,15 @@
     </row>
     <row r="4">
       <c r="A4" s="2">
-        <v>46044.0</v>
+        <v>46063.0</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="4" t="s">
         <v>10</v>
       </c>
       <c r="E4" s="3">
@@ -401,10 +419,10 @@
       <c r="B5" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="4" t="s">
         <v>12</v>
       </c>
       <c r="E5" s="3">
@@ -418,7 +436,7 @@
       <c r="B6" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D6" s="3" t="s">
@@ -433,13 +451,13 @@
         <v>46063.0</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E7" s="3">
         <v>1.0</v>
@@ -450,13 +468,13 @@
         <v>46063.0</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>6</v>
+        <v>15</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>8</v>
       </c>
       <c r="E8" s="3">
         <v>1.0</v>
@@ -467,13 +485,13 @@
         <v>46078.0</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E9" s="3">
         <v>1.0</v>
@@ -484,13 +502,13 @@
         <v>46078.0</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E10" s="3">
         <v>1.0</v>
@@ -498,18 +516,103 @@
     </row>
     <row r="11">
       <c r="A11" s="2">
-        <v>46088.0</v>
+        <v>46045.0</v>
       </c>
       <c r="B11" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E11" s="3">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2">
+        <v>46050.0</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E12" s="3">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2">
+        <v>46063.0</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E13" s="3">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2">
+        <v>46063.0</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C14" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E14" s="3">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2">
+        <v>46078.0</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E15" s="3">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2">
+        <v>46078.0</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D16" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D11" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E11" s="3">
+      <c r="E16" s="3">
         <v>1.0</v>
       </c>
     </row>
